--- a/excel/ML_Validation_Report.xlsx
+++ b/excel/ML_Validation_Report.xlsx
@@ -568,7 +568,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 25 June 2026 13:02</t>
+          <t>Generated: 26 June 2026 09:18</t>
         </is>
       </c>
     </row>
